--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.0189432498982</v>
+        <v>10.72807827810846</v>
       </c>
       <c r="D2" t="n">
-        <v>64.98268111847004</v>
+        <v>10.55968568175138</v>
       </c>
       <c r="E2" t="n">
-        <v>10.19479347343539</v>
+        <v>1.656653939433252</v>
       </c>
       <c r="F2" t="n">
-        <v>10.64798691483942</v>
+        <v>1.730297873661406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>86.40853019676898</v>
+        <v>14.04138615697496</v>
       </c>
       <c r="D3" t="n">
-        <v>86.27865494814888</v>
+        <v>14.02028142907419</v>
       </c>
       <c r="E3" t="n">
-        <v>10.19479347343539</v>
+        <v>1.656653939433252</v>
       </c>
       <c r="F3" t="n">
-        <v>10.64798691483942</v>
+        <v>1.730297873661406</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
